--- a/analysis/data/FP_FN_ALL_merged_with_discrepancies.xlsx
+++ b/analysis/data/FP_FN_ALL_merged_with_discrepancies.xlsx
@@ -22671,8 +22671,10 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28801440/</t>
         </is>
       </c>
-      <c r="P2" t="b">
-        <v>0</v>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22754,8 +22756,10 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28283496/</t>
         </is>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="S3" t="b">
         <v>1</v>
@@ -22829,11 +22833,13 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
-        </is>
-      </c>
-      <c r="P4" t="b">
-        <v>1</v>
+          <t>https://doi.org/10.19224/ai2020.196</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="S4" t="b">
         <v>1</v>
@@ -22907,11 +22913,13 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
-        </is>
-      </c>
-      <c r="P5" t="b">
-        <v>0</v>
+          <t>http://www.sciencedirect.com/science/article/pii/S0168822711700134</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22998,8 +23006,10 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/25555342/</t>
         </is>
       </c>
-      <c r="P6" t="b">
-        <v>0</v>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -23086,8 +23096,10 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/21386089/</t>
         </is>
       </c>
-      <c r="P7" t="b">
-        <v>0</v>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -23166,7 +23178,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1026/0942-5403/a000046</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S8" t="b">
@@ -23179,7 +23196,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -23239,6 +23256,19 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/24127442/</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>No longer available in DRKS, NCT00052299</t>
+        </is>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
       <c r="S9" t="b">
         <v>1</v>
       </c>
@@ -23249,7 +23279,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -23309,6 +23339,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28857576/</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S10" t="b">
         <v>0</v>
       </c>
@@ -23319,7 +23354,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -23376,7 +23411,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2015-002365-34/results</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>TrialScout is not tasked with finding summary results</t>
         </is>
       </c>
       <c r="S11" t="b">
@@ -23389,7 +23434,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -23459,6 +23504,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/30465720/</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>There is no intervention described in the publication</t>
+        </is>
+      </c>
       <c r="S12" t="b">
         <v>0</v>
       </c>
@@ -23469,7 +23524,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -23531,7 +23586,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2018.36.5_suppl.61</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S13" t="b">
@@ -23544,7 +23604,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -23614,6 +23674,19 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27098066/</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Wrong intervention, study reported through other intervention</t>
+        </is>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
       <c r="S14" t="b">
         <v>0</v>
       </c>
@@ -23624,7 +23697,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -23689,6 +23762,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/30449268/</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Weird article, "observational"</t>
+        </is>
+      </c>
       <c r="S15" t="b">
         <v>0</v>
       </c>
@@ -23699,7 +23782,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -23764,6 +23847,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/24471529/</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Not matching at all</t>
+        </is>
+      </c>
       <c r="S16" t="b">
         <v>0</v>
       </c>
@@ -23774,7 +23867,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -23844,6 +23937,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/21105988/</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>The publication is an observational study</t>
+        </is>
+      </c>
       <c r="S17" t="b">
         <v>0</v>
       </c>
@@ -23854,7 +23957,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -23916,8 +24019,24 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
-        </is>
+          <t>https://hds.hebis.de/ubgi/Record/HEB425132986</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>The results are not available anymore</t>
+        </is>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -23926,7 +24045,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -23986,6 +24105,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/26500370/</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S19" t="b">
         <v>1</v>
       </c>
@@ -23996,7 +24120,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24061,6 +24185,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/29674494/</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Abstract missing text</t>
+        </is>
+      </c>
       <c r="S20" t="b">
         <v>1</v>
       </c>
@@ -24071,7 +24205,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24136,6 +24270,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/22365373/</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S21" t="b">
         <v>1</v>
       </c>
@@ -24146,7 +24285,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24216,6 +24355,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/34224497/</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>No intervention in publication</t>
+        </is>
+      </c>
       <c r="S22" t="b">
         <v>0</v>
       </c>
@@ -24226,7 +24375,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24291,6 +24440,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28199305/</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S23" t="b">
         <v>0</v>
       </c>
@@ -24301,7 +24455,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -24371,6 +24525,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27687449/</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Explicit mention of other trial registration, duplicate?</t>
+        </is>
+      </c>
       <c r="S24" t="b">
         <v>0</v>
       </c>
@@ -24381,7 +24545,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24451,6 +24615,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/25791806/</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Explicit mention of the correct trial id</t>
+        </is>
+      </c>
       <c r="S25" t="b">
         <v>0</v>
       </c>
@@ -24461,7 +24635,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24697,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://scidok.sulb.uni-saarland.de/volltexte/2017/6827/pdf/Dissertation_ohne_Lebenslauf.pdf</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Dissertation</t>
         </is>
       </c>
       <c r="S26" t="b">
@@ -24536,7 +24720,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -24606,6 +24790,19 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/30649613/</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>It is not really trial results</t>
+        </is>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
       <c r="S27" t="b">
         <v>0</v>
       </c>
@@ -24616,7 +24813,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24686,6 +24883,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/25945807/</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Not related</t>
+        </is>
+      </c>
       <c r="S28" t="b">
         <v>0</v>
       </c>
@@ -24696,7 +24903,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24758,7 +24965,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.jcbs.2019.02.008</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S29" t="b">
@@ -24771,7 +24983,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24836,6 +25048,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/31617743/</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Completely different</t>
+        </is>
+      </c>
       <c r="S30" t="b">
         <v>0</v>
       </c>
@@ -24846,7 +25068,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -24908,7 +25130,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://d-nb.info/1141230399/34</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S31" t="b">
@@ -24921,7 +25148,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -24986,6 +25213,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/36369693/</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S32" t="b">
         <v>1</v>
       </c>
@@ -24996,7 +25228,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25056,6 +25288,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28102456/</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S33" t="b">
         <v>1</v>
       </c>
@@ -25066,7 +25303,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25128,8 +25365,16 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
-        </is>
+          <t>https://www.ostechnik.de/91-onlineartikel/5252-sensomotorische-schuheinlagen-zur-reduktion-der-sturzgefahr-bei-sturzgefaehrdeten-aelteren-menschen</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -25138,7 +25383,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25195,7 +25440,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.23736/s1973-9087.20.05921-3</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S35" t="b">
@@ -25208,7 +25458,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25273,6 +25523,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27651465/</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S36" t="b">
         <v>1</v>
       </c>
@@ -25283,7 +25538,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25600,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.mhp.2016.03.002</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S37" t="b">
@@ -25358,7 +25618,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -25420,7 +25680,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.nature.com/articles/s41598-019-43234-2</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S38" t="b">
@@ -25433,7 +25698,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25495,7 +25760,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.15761/nns.1000103</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S39" t="b">
@@ -25508,7 +25778,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25570,7 +25840,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.14283/jarcp.2019.9</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S40" t="b">
@@ -25583,7 +25858,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25653,6 +25928,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/33598644/</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>The abstract does not mention the trial</t>
+        </is>
+      </c>
       <c r="S41" t="b">
         <v>1</v>
       </c>
@@ -25663,7 +25948,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25733,6 +26018,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/23356494/</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Study protocol</t>
+        </is>
+      </c>
       <c r="S42" t="b">
         <v>0</v>
       </c>
@@ -25743,7 +26038,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25800,7 +26095,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://d-nb.info/1037829050/34</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Dissertation</t>
         </is>
       </c>
       <c r="S43" t="b">
@@ -25813,7 +26118,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -25875,7 +26180,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.2139/ssrn.3674303</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Not on pubmed</t>
         </is>
       </c>
       <c r="S44" t="b">
@@ -25888,7 +26203,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -25950,7 +26265,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.karger.com/Article/PDF/333305</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Conference abstract</t>
         </is>
       </c>
       <c r="S45" t="b">
@@ -25963,7 +26288,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -26023,6 +26348,22 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/24682512/</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Registration gone but is crossregistered to ctgov</t>
+        </is>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>Trial registration not accessible and no DRKS number in the publication or other registrations.</t>
@@ -26030,7 +26371,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26100,6 +26441,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28493040/</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Seems matching although the terminology used is different</t>
+        </is>
+      </c>
       <c r="S47" t="b">
         <v>1</v>
       </c>
@@ -26110,7 +26461,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26170,6 +26521,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/30908592/</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S48" t="b">
         <v>1</v>
       </c>
@@ -26180,7 +26536,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26245,6 +26601,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27275651/</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S49" t="b">
         <v>1</v>
       </c>
@@ -26255,7 +26616,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26320,6 +26681,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/32209619/</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S50" t="b">
         <v>1</v>
       </c>
@@ -26330,7 +26696,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26392,7 +26758,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.3238/arztebl.2018.0833</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S51" t="b">
@@ -26405,7 +26776,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26838,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2016.34.15_suppl.e21077</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S52" t="b">
@@ -26480,7 +26856,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -26537,7 +26913,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.2196/preprints.18952</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S53" t="b">
@@ -26550,7 +26931,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -26612,7 +26993,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2007-003885-16/results</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Summary results posted to the registry</t>
         </is>
       </c>
       <c r="S54" t="b">
@@ -26625,7 +27016,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26690,6 +27081,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/30962424/</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>No abstract</t>
+        </is>
+      </c>
       <c r="S55" t="b">
         <v>1</v>
       </c>
@@ -26700,7 +27101,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -26762,7 +27163,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.nmd.2013.06.580</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S56" t="b">
@@ -26775,7 +27181,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -26840,6 +27246,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/21386088/</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S57" t="b">
         <v>0</v>
       </c>
@@ -26850,7 +27261,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -26912,7 +27323,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://www.diss.fu-berlin.de/diss/servlets/MCRFileNodeServlet/FUDISS_derivate_000000019697/Habil_v.Stackelberg.pdf</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Dissertation</t>
         </is>
       </c>
       <c r="S58" t="b">
@@ -26925,7 +27346,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -26987,7 +27408,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://www.clinicsinsurgery.com/abstract.php?aid=7939</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>No pubmed</t>
         </is>
       </c>
       <c r="S59" t="b">
@@ -27000,7 +27431,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -27065,6 +27496,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/25576632/</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>No pubmed abstract</t>
+        </is>
+      </c>
       <c r="S60" t="b">
         <v>1</v>
       </c>
@@ -27075,7 +27516,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -27137,7 +27578,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2011-006314-14/results</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Summary results posted to the registry</t>
         </is>
       </c>
       <c r="S61" t="b">
@@ -27150,7 +27601,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -27215,6 +27666,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/23539216/</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Deep inside the article</t>
+        </is>
+      </c>
       <c r="S62" t="b">
         <v>1</v>
       </c>
@@ -27225,7 +27686,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -27290,6 +27751,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28012564/</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S63" t="b">
         <v>1</v>
       </c>
@@ -27300,7 +27766,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -27362,7 +27828,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2013.31.15_suppl.3586</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S64" t="b">
@@ -27375,7 +27846,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -27437,7 +27908,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.21203/rs.3.rs-28430/v1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S65" t="b">
@@ -27450,7 +27926,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -27512,7 +27988,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1101/2020.02.23.20027029</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S66" t="b">
@@ -27525,7 +28006,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -27587,7 +28068,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1093/neuonc/nov229.01</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S67" t="b">
@@ -27600,7 +28086,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -27662,7 +28148,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1055/s-0034-1395621</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Likely match</t>
         </is>
       </c>
       <c r="S68" t="b">
@@ -27675,7 +28171,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -27737,7 +28233,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.4193/RHINOL/20.022</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S69" t="b">
@@ -27750,7 +28251,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -27812,7 +28313,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2015.33.15_suppl.10056</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S70" t="b">
@@ -27825,7 +28331,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -27887,7 +28393,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://geb.uni-giessen.de/geb/volltexte/2016/12027/pdf/SetiawanBudhi_2016_03_24.pdf</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Dissertation</t>
         </is>
       </c>
       <c r="S71" t="b">
@@ -27900,7 +28416,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -27970,6 +28486,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27101285/</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Explicit link but no clinical outcomes</t>
+        </is>
+      </c>
       <c r="S72" t="b">
         <v>0</v>
       </c>
@@ -27980,7 +28506,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28568,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://purl.uni-rostock.de/fodb/pub/49779</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Dissertation</t>
         </is>
       </c>
       <c r="S73" t="b">
@@ -28055,7 +28591,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -28125,6 +28661,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/26096546/</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Explicitly mentioned in the registry but not the same intervention and not the same group</t>
+        </is>
+      </c>
       <c r="S74" t="b">
         <v>0</v>
       </c>
@@ -28135,7 +28681,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28200,6 +28746,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/22966825/</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S75" t="b">
         <v>1</v>
       </c>
@@ -28210,7 +28761,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28270,6 +28821,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/31494019/</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Wrong trial reg number in the abstract</t>
+        </is>
+      </c>
       <c r="S76" t="b">
         <v>1</v>
       </c>
@@ -28280,7 +28841,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28345,6 +28906,19 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27555381/</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Close but no match, no pharmacological component</t>
+        </is>
+      </c>
+      <c r="R77" t="b">
+        <v>1</v>
+      </c>
       <c r="S77" t="b">
         <v>0</v>
       </c>
@@ -28355,7 +28929,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28425,6 +28999,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/23530026/</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Does not match time</t>
+        </is>
+      </c>
       <c r="S78" t="b">
         <v>1</v>
       </c>
@@ -28435,7 +29019,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -28500,6 +29084,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/33456728/</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S79" t="b">
         <v>1</v>
       </c>
@@ -28510,7 +29099,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28580,6 +29169,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27609788/</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Pub is phase 1 first in man, reg is phase 2</t>
+        </is>
+      </c>
       <c r="S80" t="b">
         <v>0</v>
       </c>
@@ -28590,7 +29189,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28660,6 +29259,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/25613108/</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Non interventional pub</t>
+        </is>
+      </c>
       <c r="S81" t="b">
         <v>0</v>
       </c>
@@ -28670,7 +29279,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28740,6 +29349,19 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28114352/</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Slightly different intervention</t>
+        </is>
+      </c>
+      <c r="R82" t="b">
+        <v>1</v>
+      </c>
       <c r="S82" t="b">
         <v>0</v>
       </c>
@@ -28750,7 +29372,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -28815,6 +29437,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/31354424/</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S83" t="b">
         <v>1</v>
       </c>
@@ -28825,7 +29452,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28887,7 +29514,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2014-003746-27/results</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Summary results posted to the registry</t>
         </is>
       </c>
       <c r="S84" t="b">
@@ -28900,7 +29537,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -28962,7 +29599,12 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.idairyj.2018.05.017</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S85" t="b">
@@ -28975,7 +29617,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29679,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://opendata.uni-halle.de/bitstream/1981185920/14231/1/Dissertation%20Rucker%20Alfred%20ML.pdf</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Dissertation</t>
         </is>
       </c>
       <c r="S86" t="b">
@@ -29050,7 +29702,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -29120,6 +29772,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/30649613/</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Different outcome</t>
+        </is>
+      </c>
       <c r="S87" t="b">
         <v>0</v>
       </c>
@@ -29130,7 +29792,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29195,6 +29857,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/21929562/</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Reg is for phase 3 study and started after</t>
+        </is>
+      </c>
       <c r="S88" t="b">
         <v>0</v>
       </c>
@@ -29205,7 +29877,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29275,6 +29947,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/33783307/</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>No abstract available</t>
+        </is>
+      </c>
       <c r="S89" t="b">
         <v>0</v>
       </c>
@@ -29285,7 +29967,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -29355,6 +30037,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/23006429/</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>No intervention in publication</t>
+        </is>
+      </c>
       <c r="S90" t="b">
         <v>0</v>
       </c>
@@ -29365,7 +30057,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29430,6 +30122,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/27064493/</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S91" t="b">
         <v>1</v>
       </c>
@@ -29440,7 +30137,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29505,6 +30202,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/31013466/</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S92" t="b">
         <v>1</v>
       </c>
@@ -29515,7 +30217,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29580,6 +30282,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/29502304/</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>TrialScout didn't find the article which is strange. This was due to incorrect metadata which caused it to be filtered during validation.</t>
+        </is>
+      </c>
       <c r="S93" t="b">
         <v>1</v>
       </c>
@@ -29590,7 +30302,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29660,6 +30372,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/31157299/</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S94" t="b">
         <v>0</v>
       </c>
@@ -29670,7 +30387,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -29735,6 +30452,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/31453846/</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S95" t="b">
         <v>1</v>
       </c>
@@ -29745,7 +30467,7 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29807,7 +30529,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://digibib.hs-nb.de/file/dbhsnb_derivate_0000002256/Bachelorarbeit-Baecker-2017.pdf</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Bachelor paper</t>
         </is>
       </c>
       <c r="S96" t="b">
@@ -29820,7 +30552,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -29880,6 +30612,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/28990261/</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S97" t="b">
         <v>1</v>
       </c>
@@ -29890,7 +30627,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -29960,6 +30697,16 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/24907384/</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Subanalysis, not main outcome</t>
+        </is>
+      </c>
       <c r="S98" t="b">
         <v>0</v>
       </c>
@@ -29970,7 +30717,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -30032,7 +30779,12 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.14283/jarcp.2017.27</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S99" t="b">
@@ -30045,7 +30797,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
@@ -30107,8 +30859,21 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
-        </is>
+          <t>http://www.gjpsy.uni-goettingen.de/gjp-article-kiermeir.pdf</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>No publication available anymore</t>
+        </is>
+      </c>
+      <c r="S100" t="b">
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -30117,7 +30882,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -30182,6 +30947,11 @@
           <t>https://pubmed.ncbi.nlm.nih.gov/31275188/</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="S101" t="b">
         <v>0</v>
       </c>
@@ -30192,7 +30962,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Disagreement</t>
         </is>
       </c>
     </row>
@@ -30254,7 +31024,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://geb.uni-giessen.de/geb/volltexte/2011/8475/pdf/WaldAnke_2011_11_24.pdf</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -30316,7 +31086,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1186/s41044-017-0027-3</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -30378,7 +31148,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.4236/health.2017.101003</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -30445,7 +31215,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.21203/rs.3.rs-1560793/v1</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -30512,7 +31282,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://www.themedicinescompany.com/investors/news/medicines-company-discontinues-phase-2b-trial-mdco-2010</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -30579,7 +31349,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1002/tsm2.32</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -30914,7 +31684,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1007/s10803-020-04471-x</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -31048,7 +31818,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://www.jns-journal.com/article/S0022-510X(13)01543-8/fulltext</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -31115,7 +31885,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/S0016-5085(20)32103-X</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -31244,7 +32014,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2011-004361-32/results</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -31445,7 +32215,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.4236/ojts.2012.23014</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -31718,7 +32488,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1136/jnnp-2014-309032.294</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -31847,7 +32617,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.2174/18746136-v16-e2206200</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -31976,7 +32746,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1080/15289168.2015.1014991</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -32115,7 +32885,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://www.bloodjournal.org/content/124/21/3986</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -32254,7 +33024,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1093/schbul/sby016.317</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -32321,7 +33091,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.12688/f1000research.73698.1</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -32388,7 +33158,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2005-004675-37/results</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -32455,7 +33225,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.ijosm.2016.03.002</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -32589,7 +33359,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2009-015929-37/results</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -32790,7 +33560,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1186/cc14575</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -32857,7 +33627,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1017/S1460396921000078</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -32924,7 +33694,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://digital.bibliothek.uni-halle.de/ulbhalhs/urn/urn:nbn:de:gbv:3:4-18063</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -33202,7 +33972,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://epub.ub.uni-greifswald.de/frontdoor/deliver/index/docId/1997/file/diss_Hasan_Mahmoud.pdf</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -33408,7 +34178,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.idairyj.2017.11.011</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -33475,7 +34245,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://iovs.arvojournals.org/article.aspx?articleid=2363769</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -33542,7 +34312,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.eujim.2016.06.015</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -33609,7 +34379,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2007-000241-35/results</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -33815,7 +34585,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://ash.confex.com/ash/2017/webprogram/Paper99881.html</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -33882,7 +34652,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1007/s00262-019-02383-z</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -34011,7 +34781,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://www.bloodjournal.org/content/120/21/5029?sso-checked=true</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -34078,7 +34848,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2008-003064-19/results</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -34413,7 +35183,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.21203/rs.3.rs-557545/v1</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
@@ -34480,7 +35250,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.13140/rg.2.2.19672.85765</t>
         </is>
       </c>
       <c r="U165" t="inlineStr">
@@ -34614,7 +35384,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2011-000801-39/results</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -34748,7 +35518,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.4126/frl01-006416711</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
@@ -34944,7 +35714,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.15761/GVI.1000125</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -35011,7 +35781,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.researchsquare.com/article/rs-34469/v1</t>
         </is>
       </c>
       <c r="U173" t="inlineStr">
@@ -35078,7 +35848,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2017.35.15_suppl.2046</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
@@ -35207,7 +35977,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.tacc.2018.01.003</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
@@ -35408,7 +36178,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2011-001819-30/results</t>
         </is>
       </c>
       <c r="U179" t="inlineStr">
@@ -35542,7 +36312,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://iovs.arvojournals.org/article.aspx?articleid=2373309</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
@@ -35681,7 +36451,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://elibrary.klett-cotta.de/article/99.120110/aep-8-3-175</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
@@ -35887,7 +36657,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/s0959-8049(11)70845-0</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
@@ -36289,7 +37059,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://docserv.uni-duesseldorf.de/servlets/DerivateServlet/Derivate-50771/Boschek%2C%20Lisa%20Charlotte_Dissertation.pdf</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
@@ -36557,7 +37327,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1177/0143034320958743</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
@@ -37026,7 +37796,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.bundesgesundheitsministerium.de/fileadmin/Dateien/5_Publikationen/Gesundheit/Berichte/Abschlussbericht_VEMSE-190416.pdf</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
@@ -37227,7 +37997,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.bbmt.2011.12.041</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
@@ -37361,7 +38131,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://macau.uni-kiel.de/receive/diss_mods_00026102</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -37629,7 +38399,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://edoc.ub.uni-muenchen.de/26157/1/Schuetz_Swetlana.pdf</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -37763,7 +38533,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2018.36.15_suppl.e17553</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
@@ -37897,7 +38667,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2008-002302-18/results</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
@@ -37964,7 +38734,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://opendata.uni-halle.de/bitstream/1981185920/8487/1/Dissertation%20Baier%20J%C3%BCrgen%2023.3.2016.pdf</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -38031,7 +38801,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2011-004304-38/results</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
@@ -38165,7 +38935,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1055/s-0037-1607119</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
@@ -38299,7 +39069,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.12968/ijtr.2018.0057</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -38572,7 +39342,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1136/annrheumdis-2016-eular.2780</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
@@ -38711,7 +39481,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.jff.2019.103443</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
@@ -38835,7 +39605,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1080/19012276.2021.2020683</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
@@ -38902,7 +39672,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>lucris.lub.lu.se/ws/portalfiles/portal/51010099/Yoghatama_Cindya_Zanzer_PhD_thesis.pdf</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
@@ -38969,7 +39739,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2008-001443-19/results</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
@@ -39165,7 +39935,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1108/he-11-2016-0061</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
@@ -39232,7 +40002,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.invent.2014.12.003</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
@@ -39639,7 +40409,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.13188/2377-9284.1000003</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
@@ -39706,7 +40476,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicsofsurgery.com/uploads/COS-v2-1032.pdf</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
@@ -39773,7 +40543,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.eujim.2012.04.001</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
@@ -39835,7 +40605,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1055/a-0842-6901</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
@@ -39902,7 +40672,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1007/s11145-016-9632-1</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
@@ -40381,7 +41151,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.ejtd.2022.100277</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
@@ -40448,7 +41218,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.21203/rs.2.20336/v1</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
@@ -40850,7 +41620,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://mediatum.ub.tum.de/1304544</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
@@ -40917,7 +41687,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>http://iovs.arvojournals.org/article.aspx?articleid=2351700</t>
         </is>
       </c>
       <c r="U261" t="inlineStr">
@@ -41190,7 +41960,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1182/blood-2018-99-110429</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
@@ -41257,7 +42027,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/s1359-6349(09)71339-4</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
@@ -41324,7 +42094,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.4172/2167-0846.1000343</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
@@ -41525,7 +42295,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1158/1538-7445.am2016-3269</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
@@ -41659,7 +42429,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1002/ygh2.489</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
@@ -42086,7 +42856,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.29011/2575-9760.001328</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
@@ -42225,7 +42995,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.15496/publikation-24421</t>
         </is>
       </c>
       <c r="U280" t="inlineStr">
@@ -42354,7 +43124,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2015-002098-40/results</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
@@ -42421,7 +43191,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/s0167-8140(15)30355-8</t>
         </is>
       </c>
       <c r="U283" t="inlineStr">
@@ -42555,7 +43325,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.researchgate.net/publication/264848719_DermaVir_for_initial_treatment_of_HIV-infected_subjects_demonstrates_preliminary_safety_immunogenicity_and_HIV-RNA_reduction_versus_placebo_immunization_A-240-0111-_12561</t>
         </is>
       </c>
       <c r="U285" t="inlineStr">
@@ -42684,7 +43454,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.25673/32106</t>
         </is>
       </c>
       <c r="U287" t="inlineStr">
@@ -42751,7 +43521,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1101/2022.01.31.22269313</t>
         </is>
       </c>
       <c r="U288" t="inlineStr">
@@ -42885,7 +43655,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://static1.squarespace.com/static/5f625d72f543114733b9e43e/t/60363993a88c79395f201173/1614166419994/3+RP+Foster+Care.pdf</t>
         </is>
       </c>
       <c r="U290" t="inlineStr">
@@ -43019,7 +43789,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://pdfs.semanticscholar.org/b3a6/c8239a9c030a1c7a3af8acbafc77c9a8ecc2.pdf?_ga=2.264204238.316868046.1597691860-1172082013.1597691860</t>
         </is>
       </c>
       <c r="U292" t="inlineStr">
@@ -43153,7 +43923,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1016/j.chb.2015.08.027</t>
         </is>
       </c>
       <c r="U294" t="inlineStr">
@@ -43220,7 +43990,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2013.31.15_suppl.3625</t>
         </is>
       </c>
       <c r="U295" t="inlineStr">
@@ -43287,7 +44057,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2012-003229-91/results</t>
         </is>
       </c>
       <c r="U296" t="inlineStr">
@@ -43354,7 +44124,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.24015/JAPM.2017.0049</t>
         </is>
       </c>
       <c r="U297" t="inlineStr">
@@ -43421,7 +44191,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.researchgate.net/publication/327302891_Neue_DWI-Lasionen_beim_Carotisstent_mit_und_ohne_proximales_Protektionssystem</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -43833,7 +44603,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.1200/jco.2016.34.15_suppl.11004</t>
         </is>
       </c>
       <c r="U304" t="inlineStr">
@@ -43900,7 +44670,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://doi.org/10.12691/jfnr-8-12-7</t>
         </is>
       </c>
       <c r="U305" t="inlineStr">
@@ -43967,7 +44737,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/NA/</t>
+          <t>https://www.clinicaltrialsregister.eu/ctr-search/trial/2010-022854-18/results</t>
         </is>
       </c>
       <c r="U306" t="inlineStr">
